--- a/backend/src/main/resources/templates/init-ap-template.xlsx
+++ b/backend/src/main/resources/templates/init-ap-template.xlsx
@@ -46,7 +46,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -54,10 +54,11 @@
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:6">
+    <row r="1" ht="30" customHeight="1" spans="1:7">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">供应商编码</t>
@@ -78,19 +79,24 @@
           <t xml:space="preserve">原单据日期</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">应付金额</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">期初预付金额</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">备注</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:G1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -98,7 +104,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -107,7 +113,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">供应商应付期初导入模板</t>
+          <t xml:space="preserve">供应商应付/预付期初导入模板</t>
         </is>
       </c>
     </row>
@@ -142,7 +148,7 @@
     <row r="6" ht="19" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4. 数字不要加千分位、货币符号；金额/数量直接填数字。</t>
+          <t xml:space="preserve">4. 数字不要加千分位、货币符号；金额直接填数字。</t>
         </is>
       </c>
     </row>
@@ -163,42 +169,49 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">供应商应付期初填写规则</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="19" customHeight="1">
+          <t xml:space="preserve">供应商应付/预付期初填写规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. 必填列：供应商编码、应付金额。供应商编码必须是供应商档案中已存在的编码。</t>
+          <t xml:space="preserve">1. 必填列：供应商编码（必须是供应商档案中已存在的编码）；每行「应付金额」「期初预付金额」至少一项大于 0，两项可同时填写（同供应商同时存在应付与预付时各填各的，不做轧差）。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. 应付金额为截至建账日的未付款余额（含税口径），必须大于 0，最多 2 位小数；系统只导入未达余额，不编造历史付款与核销记录。</t>
+          <t xml:space="preserve">2. 应付金额为截至建账日的未付款余额（含税口径），≥0、最多 2 位小数；过账后生成 QCAP 应付单，账龄自建账日起算，到期日统一为建账日 + 30 天。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. 原单据号、原单据日期仅留存备查，不进入正式往来账：账龄统一从建账日起算，到期日统一为建账日 + 30 天。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="19" customHeight="1">
+          <t xml:space="preserve">3. 期初预付金额为截至建账日已预付给供应商的余额，≥0、最多 2 位小数；过账后只登记供应商账户预付余额（QCYF 期初流水），不生成付款单、不影响资金账户。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4. 同一文件内「供应商+原单据号」不能重复；原单据号为空时同一供应商只能出现一行，请先在表内合并金额。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="19" customHeight="1">
+          <t xml:space="preserve">4. 原单据号、原单据日期仅留存备查，不进入正式往来账。同一文件内「供应商+原单据号」不能重复；原单据号为空时同一供应商只能出现一行，请先在表内合并金额。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5. 反建账限制：行生成的应付单一旦被付款核销或产生核销记录，则不能反建账。</t>
+          <t xml:space="preserve">5. 反建账限制：行生成的应付单一经付款核销或产生核销记录不能反建账；行生成的期初预付流水一旦被预付核销、预付退款或厂家费用转预付占用，也不能反建账。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6. 上线后补录预付请用「供应商应付期初」页面的「预付补录」功能（独立批号、当日未封账且总账当月未月结），不要在本模板中补录。</t>
         </is>
       </c>
     </row>
